--- a/reports/Leetcode Daily Report 3 year_2026-09-11.xlsx
+++ b/reports/Leetcode Daily Report 3 year_2026-09-11.xlsx
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45">
